--- a/resources/library/xlsx/break-even-analysis.xlsx
+++ b/resources/library/xlsx/break-even-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" r:id="R80ca1eb94b714556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R43a8550e564d494b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="Rf7e9ae4d00e44357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" r:id="R858330b2c2c64429"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R38c35088497f4963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R17b9b82dc8d34d76"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -162,6 +162,102 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="4acd9b69-06a8-45ad-b732-5e7eadaf84c7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R96cc54e02fc44915"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="26b4fdb0-da89-4b6b-895f-67b8fe549f38"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb6f79d6e9dae437c"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="b8a1d4cd-f4de-4674-82c6-313be7c415b5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R61180fc0012a48fc"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -359,7 +455,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="48" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1432,6 +1528,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24b6f8f53d6e4861"/>
 </x:worksheet>
 </file>
 
@@ -1446,7 +1543,7 @@
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="15"/>
       <x:c r="B1" s="15"/>
       <x:c r="C1" s="15"/>
@@ -2507,6 +2604,7 @@
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb071b35f2454a04"/>
 </x:worksheet>
 </file>
 
@@ -2521,7 +2619,7 @@
     <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="15"/>
       <x:c r="B1" s="15"/>
       <x:c r="C1" s="15"/>
@@ -3583,5 +3681,6 @@
     <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79a4b16da93d4058"/>
 </x:worksheet>
 </file>